--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.69</v>
+        <v>46.31</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.58</v>
+        <v>24.48</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.95</v>
+        <v>36.35</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>60.39</v>
+        <v>60.01</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.59</v>
+        <v>30.94</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.16</v>
+        <v>44.8</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.1</v>
+        <v>27.64</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.28</v>
+        <v>23.95</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>183.15</v>
+        <v>184.36</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>201.93</v>
+        <v>203</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>246.54</v>
+        <v>245.55</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>38.95</v>
+        <v>38.44</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>29.3</v>
+        <v>29.29</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>34.52</v>
+        <v>34.26</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>48.75</v>
+        <v>48.2</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.72</v>
+        <v>33.45</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>36.03</v>
+        <v>36</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>232.93</v>
+        <v>225.11</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>27.95</v>
+        <v>27.9</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.508</v>
+        <v>4.493</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.818</v>
+        <v>3.784</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.69</v>
+        <v>46.31</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.58</v>
+        <v>24.48</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.95</v>
+        <v>36.35</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>60.39</v>
+        <v>60.01</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.59</v>
+        <v>30.94</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.16</v>
+        <v>44.8</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.1</v>
+        <v>27.64</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.28</v>
+        <v>23.95</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>183.15</v>
+        <v>184.36</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>246.54</v>
+        <v>245.55</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>201.93</v>
+        <v>203</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>324.8</v>
+        <v>312.15</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>38.95</v>
+        <v>38.44</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>29.3</v>
+        <v>29.29</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>34.52</v>
+        <v>34.26</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>48.75</v>
+        <v>48.2</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.72</v>
+        <v>33.45</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>36.03</v>
+        <v>36</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>232.93</v>
+        <v>225.11</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>27.95</v>
+        <v>27.9</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.508</v>
+        <v>4.493</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.305</v>
+        <v>1.299</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.818</v>
+        <v>3.784</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.31</v>
+        <v>46.46</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.48</v>
+        <v>24.7</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.35</v>
+        <v>36.56</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>60.01</v>
+        <v>61.13</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.94</v>
+        <v>31.68</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.8</v>
+        <v>49</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>27.64</v>
+        <v>29.41</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>23.95</v>
+        <v>24.86</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>184.36</v>
+        <v>183</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>203</v>
+        <v>201.04</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>245.55</v>
+        <v>242.55</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.926</v>
+        <v>0.922</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>38.44</v>
+        <v>37.82</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>29.29</v>
+        <v>30.36</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>34.26</v>
+        <v>34.2</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.45</v>
+        <v>33.64</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>36</v>
+        <v>35.47</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>225.11</v>
+        <v>226.12</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>27.9</v>
+        <v>28.57</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.493</v>
+        <v>4.521</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.784</v>
+        <v>3.801</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.31</v>
+        <v>46.46</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.48</v>
+        <v>24.7</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.35</v>
+        <v>36.56</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>60.01</v>
+        <v>61.13</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.94</v>
+        <v>31.68</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.8</v>
+        <v>49</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>27.64</v>
+        <v>29.41</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>23.95</v>
+        <v>24.86</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>184.36</v>
+        <v>183</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>245.55</v>
+        <v>242.55</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>203</v>
+        <v>201.04</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>312.15</v>
+        <v>308.9</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.926</v>
+        <v>0.922</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>38.44</v>
+        <v>37.82</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>29.29</v>
+        <v>30.36</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>34.26</v>
+        <v>34.2</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.45</v>
+        <v>33.64</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>36</v>
+        <v>35.47</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>225.11</v>
+        <v>226.12</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>27.9</v>
+        <v>28.57</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.493</v>
+        <v>4.521</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.299</v>
+        <v>1.308</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.784</v>
+        <v>3.801</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.46</v>
+        <v>46.61</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.7</v>
+        <v>24.81</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.56</v>
+        <v>36.12</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>61.13</v>
+        <v>60.84</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.68</v>
+        <v>31.36</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>49</v>
+        <v>47.52</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.41</v>
+        <v>29.6</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.86</v>
+        <v>25.35</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>183</v>
+        <v>182.5</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>201.04</v>
+        <v>198.61</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>242.55</v>
+        <v>244</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.922</v>
+        <v>0.913</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>13</v>
+        <v>12.71</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>37.82</v>
+        <v>37.38</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>30.36</v>
+        <v>29.82</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>34.2</v>
+        <v>33.67</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>48.1</v>
+        <v>47.25</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.64</v>
+        <v>33.17</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>35.47</v>
+        <v>34.28</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>226.12</v>
+        <v>220.91</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>28.57</v>
+        <v>27.5</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.521</v>
+        <v>4.511</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.801</v>
+        <v>3.797</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.46</v>
+        <v>46.61</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.7</v>
+        <v>24.81</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.56</v>
+        <v>36.12</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>61.13</v>
+        <v>60.84</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.68</v>
+        <v>31.36</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>49</v>
+        <v>47.52</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.41</v>
+        <v>29.6</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.86</v>
+        <v>25.35</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>183</v>
+        <v>182.5</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>242.55</v>
+        <v>244</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>201.04</v>
+        <v>198.61</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>308.9</v>
+        <v>306.24</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.922</v>
+        <v>0.913</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>13</v>
+        <v>12.71</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>37.82</v>
+        <v>37.38</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.36</v>
+        <v>29.82</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>34.2</v>
+        <v>33.67</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>48.1</v>
+        <v>47.25</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.64</v>
+        <v>33.17</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>35.47</v>
+        <v>34.28</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>226.12</v>
+        <v>220.91</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>28.57</v>
+        <v>27.5</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.521</v>
+        <v>4.511</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.801</v>
+        <v>3.797</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.61</v>
+        <v>45.85</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.81</v>
+        <v>24.29</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.12</v>
+        <v>35.38</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>60.84</v>
+        <v>59.52</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.36</v>
+        <v>30.62</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>47.52</v>
+        <v>45</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.6</v>
+        <v>28.63</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.35</v>
+        <v>24.83</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>182.5</v>
+        <v>179.73</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>198.61</v>
+        <v>194.74</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>244</v>
+        <v>235.34</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.913</v>
+        <v>0.888</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.71</v>
+        <v>12.58</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>37.38</v>
+        <v>37.02</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>29.82</v>
+        <v>28.95</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>33.67</v>
+        <v>32.89</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>47.25</v>
+        <v>47.45</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.17</v>
+        <v>32.81</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.28</v>
+        <v>33.85</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>220.91</v>
+        <v>209.49</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>27.5</v>
+        <v>27.81</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.511</v>
+        <v>4.452</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.797</v>
+        <v>3.725</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>46.61</v>
+        <v>45.85</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.81</v>
+        <v>24.29</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.12</v>
+        <v>35.38</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>60.84</v>
+        <v>59.52</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>31.36</v>
+        <v>30.62</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>47.52</v>
+        <v>45</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.6</v>
+        <v>28.63</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.35</v>
+        <v>24.83</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>182.5</v>
+        <v>179.73</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>244</v>
+        <v>235.34</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>198.61</v>
+        <v>194.74</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>306.24</v>
+        <v>298.2</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.913</v>
+        <v>0.888</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.71</v>
+        <v>12.58</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>37.38</v>
+        <v>37.02</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>29.82</v>
+        <v>28.95</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>33.67</v>
+        <v>32.89</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>47.25</v>
+        <v>47.45</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.17</v>
+        <v>32.81</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>34.28</v>
+        <v>33.85</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>220.91</v>
+        <v>209.49</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>27.5</v>
+        <v>27.81</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.511</v>
+        <v>4.452</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.308</v>
+        <v>1.285</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.797</v>
+        <v>3.725</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.85</v>
+        <v>45.6</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.29</v>
+        <v>24.02</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>35.38</v>
+        <v>35.59</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>59.52</v>
+        <v>59.01</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.62</v>
+        <v>30.71</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45</v>
+        <v>45.33</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.63</v>
+        <v>28.8</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.83</v>
+        <v>24.92</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>179.73</v>
+        <v>177.95</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>194.74</v>
+        <v>191.59</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>235.34</v>
+        <v>235.05</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.888</v>
+        <v>0.887</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.58</v>
+        <v>12.54</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>37.02</v>
+        <v>36.62</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>28.95</v>
+        <v>28.56</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>32.89</v>
+        <v>32.18</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>47.45</v>
+        <v>46.27</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>32.81</v>
+        <v>32.89</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.85</v>
+        <v>33.06</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>209.49</v>
+        <v>209.41</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>27.81</v>
+        <v>26.96</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.452</v>
+        <v>4.468</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.725</v>
+        <v>3.676</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.85</v>
+        <v>45.6</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.29</v>
+        <v>24.02</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>35.38</v>
+        <v>35.59</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>59.52</v>
+        <v>59.01</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.62</v>
+        <v>30.71</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45</v>
+        <v>45.33</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.63</v>
+        <v>28.8</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.83</v>
+        <v>24.92</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>179.73</v>
+        <v>177.95</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>235.34</v>
+        <v>235.05</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>194.74</v>
+        <v>191.59</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>298.2</v>
+        <v>299.6</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.888</v>
+        <v>0.887</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.58</v>
+        <v>12.54</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>37.02</v>
+        <v>36.62</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>28.95</v>
+        <v>28.56</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>32.89</v>
+        <v>32.18</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>47.45</v>
+        <v>46.27</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>32.81</v>
+        <v>32.89</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>33.85</v>
+        <v>33.06</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>209.49</v>
+        <v>209.41</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>27.81</v>
+        <v>26.96</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.452</v>
+        <v>4.468</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.285</v>
+        <v>1.294</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.725</v>
+        <v>3.676</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.6</v>
+        <v>45.82</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.02</v>
+        <v>24.27</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>35.59</v>
+        <v>37.99</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>59.01</v>
+        <v>59.16</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.71</v>
+        <v>30.81</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.33</v>
+        <v>45.7</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.92</v>
+        <v>25.12</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>177.95</v>
+        <v>178.64</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>191.59</v>
+        <v>192.7</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>235.05</v>
+        <v>240.97</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.887</v>
+        <v>0.891</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.54</v>
+        <v>12.38</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.62</v>
+        <v>36.34</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>28.56</v>
+        <v>28.4</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>32.18</v>
+        <v>31.61</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>46.27</v>
+        <v>45.14</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>32.89</v>
+        <v>33.4</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.06</v>
+        <v>33.2</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>209.41</v>
+        <v>211.97</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.96</v>
+        <v>26.65</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.468</v>
+        <v>4.464</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.676</v>
+        <v>3.669</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.6</v>
+        <v>45.82</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.02</v>
+        <v>24.27</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>35.59</v>
+        <v>37.99</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>59.01</v>
+        <v>59.16</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.71</v>
+        <v>30.81</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.33</v>
+        <v>45.7</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.92</v>
+        <v>25.12</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>177.95</v>
+        <v>178.64</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>235.05</v>
+        <v>240.97</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>191.59</v>
+        <v>192.7</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>299.6</v>
+        <v>300.77</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.887</v>
+        <v>0.891</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.54</v>
+        <v>12.38</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.62</v>
+        <v>36.34</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>28.56</v>
+        <v>28.4</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>32.18</v>
+        <v>31.61</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>46.27</v>
+        <v>45.14</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>32.89</v>
+        <v>33.4</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>33.06</v>
+        <v>33.2</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>209.41</v>
+        <v>211.97</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.96</v>
+        <v>26.65</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.468</v>
+        <v>4.464</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.294</v>
+        <v>1.289</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.676</v>
+        <v>3.669</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.82</v>
+        <v>45.38</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.27</v>
+        <v>24.08</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.99</v>
+        <v>37.8</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>59.16</v>
+        <v>58.22</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.81</v>
+        <v>30.87</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.7</v>
+        <v>44.9</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.9</v>
+        <v>28.74</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.12</v>
+        <v>25.74</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>178.64</v>
+        <v>175.18</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>192.7</v>
+        <v>189.38</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>240.97</v>
+        <v>234.2</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.891</v>
+        <v>0.871</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.38</v>
+        <v>12.02</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.34</v>
+        <v>36.11</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>28.4</v>
+        <v>28.18</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>31.61</v>
+        <v>31</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>45.14</v>
+        <v>44.91</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.4</v>
+        <v>33.99</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>211.97</v>
+        <v>207.35</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.65</v>
+        <v>26.43</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.464</v>
+        <v>4.388</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.82</v>
+        <v>45.38</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.27</v>
+        <v>24.08</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.99</v>
+        <v>37.8</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>59.16</v>
+        <v>58.22</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.81</v>
+        <v>30.87</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.7</v>
+        <v>44.9</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.9</v>
+        <v>28.74</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.12</v>
+        <v>25.74</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>178.64</v>
+        <v>175.18</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>240.97</v>
+        <v>234.2</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>192.7</v>
+        <v>189.38</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>300.77</v>
+        <v>293.2</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.891</v>
+        <v>0.871</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.38</v>
+        <v>12.02</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.34</v>
+        <v>36.11</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>28.4</v>
+        <v>28.18</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>31.61</v>
+        <v>31</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>45.14</v>
+        <v>44.91</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.4</v>
+        <v>33.99</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>211.97</v>
+        <v>207.35</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.65</v>
+        <v>26.43</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.464</v>
+        <v>4.388</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.289</v>
+        <v>1.266</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.38</v>
+        <v>45.51</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.08</v>
+        <v>24</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.8</v>
+        <v>38.12</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>58.22</v>
+        <v>56.51</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.87</v>
+        <v>30.11</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.9</v>
+        <v>44.18</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.74</v>
+        <v>28.76</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.74</v>
+        <v>24.82</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>175.18</v>
+        <v>173.44</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>189.38</v>
+        <v>190</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>234.2</v>
+        <v>234.53</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.871</v>
+        <v>0.863</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.02</v>
+        <v>11.95</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.11</v>
+        <v>36.38</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>28.18</v>
+        <v>28.09</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>31</v>
+        <v>29.95</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>44.91</v>
+        <v>43.8</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.99</v>
+        <v>34.93</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.5</v>
+        <v>33.28</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>207.35</v>
+        <v>203.54</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.43</v>
+        <v>26.02</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.388</v>
+        <v>4.352</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.669</v>
+        <v>3.668</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.38</v>
+        <v>45.51</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.08</v>
+        <v>24</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.8</v>
+        <v>38.12</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>58.22</v>
+        <v>56.51</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.87</v>
+        <v>30.11</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.9</v>
+        <v>44.18</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.74</v>
+        <v>28.76</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.74</v>
+        <v>24.82</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>175.18</v>
+        <v>173.44</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>234.2</v>
+        <v>234.53</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>189.38</v>
+        <v>190</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>293.2</v>
+        <v>290.39</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.871</v>
+        <v>0.863</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.02</v>
+        <v>11.95</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.11</v>
+        <v>36.38</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>28.18</v>
+        <v>28.09</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>31</v>
+        <v>29.95</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>44.91</v>
+        <v>43.8</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.99</v>
+        <v>34.93</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>33.5</v>
+        <v>33.28</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>207.35</v>
+        <v>203.54</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.43</v>
+        <v>26.02</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.388</v>
+        <v>4.352</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.266</v>
+        <v>1.259</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.669</v>
+        <v>3.668</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.51</v>
+        <v>45.08</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24</v>
+        <v>23.88</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>38.12</v>
+        <v>37.54</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.51</v>
+        <v>56.3</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.11</v>
+        <v>29.95</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.18</v>
+        <v>45.77</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.76</v>
+        <v>28.47</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.82</v>
+        <v>25.07</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>173.44</v>
+        <v>173.4</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>190</v>
+        <v>193.1</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>234.53</v>
+        <v>237</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.863</v>
+        <v>0.87</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.95</v>
+        <v>11.99</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.38</v>
+        <v>35.96</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>28.09</v>
+        <v>27.88</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>29.95</v>
+        <v>30.02</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>43.8</v>
+        <v>45.39</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.93</v>
+        <v>34.97</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.28</v>
+        <v>32.94</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>203.54</v>
+        <v>205.6</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.02</v>
+        <v>26.79</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.352</v>
+        <v>4.359</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.668</v>
+        <v>3.646</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.51</v>
+        <v>45.08</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24</v>
+        <v>23.88</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>38.12</v>
+        <v>37.54</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.51</v>
+        <v>56.3</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>30.11</v>
+        <v>29.95</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.18</v>
+        <v>45.77</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.76</v>
+        <v>28.47</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.82</v>
+        <v>25.07</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>173.44</v>
+        <v>173.4</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>234.53</v>
+        <v>237</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>190</v>
+        <v>193.1</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>290.39</v>
+        <v>289.76</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.863</v>
+        <v>0.87</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.95</v>
+        <v>11.99</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.38</v>
+        <v>35.96</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>28.09</v>
+        <v>27.88</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>29.95</v>
+        <v>30.02</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>43.8</v>
+        <v>45.39</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.93</v>
+        <v>34.97</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>33.28</v>
+        <v>32.94</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>203.54</v>
+        <v>205.6</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.02</v>
+        <v>26.79</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.352</v>
+        <v>4.359</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.259</v>
+        <v>1.262</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.668</v>
+        <v>3.646</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.08</v>
+        <v>43.6</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.88</v>
+        <v>23.98</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.54</v>
+        <v>37.36</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.3</v>
+        <v>56.77</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.95</v>
+        <v>29.6</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.77</v>
+        <v>46.24</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.47</v>
+        <v>29.47</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.07</v>
+        <v>24.88</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>173.4</v>
+        <v>173.01</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>193.1</v>
+        <v>190.13</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>237</v>
+        <v>234.28</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.87</v>
+        <v>0.863</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.99</v>
+        <v>11.93</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>35.96</v>
+        <v>36.09</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>27.88</v>
+        <v>27.32</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.02</v>
+        <v>29.63</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>45.39</v>
+        <v>44.94</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.97</v>
+        <v>34.18</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>32.94</v>
+        <v>29.98</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>205.6</v>
+        <v>209.5</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.79</v>
+        <v>26.7</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.359</v>
+        <v>4.36</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.646</v>
+        <v>3.647</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>45.08</v>
+        <v>43.6</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.88</v>
+        <v>23.98</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.54</v>
+        <v>37.36</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.3</v>
+        <v>56.77</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.95</v>
+        <v>29.6</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.77</v>
+        <v>46.24</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.47</v>
+        <v>29.47</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>25.07</v>
+        <v>24.88</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>173.4</v>
+        <v>173.01</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>237</v>
+        <v>234.28</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>193.1</v>
+        <v>190.13</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>289.76</v>
+        <v>288.42</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.87</v>
+        <v>0.863</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.99</v>
+        <v>11.93</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>35.96</v>
+        <v>36.09</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>27.88</v>
+        <v>27.32</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>30.02</v>
+        <v>29.63</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>45.39</v>
+        <v>44.94</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.97</v>
+        <v>34.18</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>32.94</v>
+        <v>29.98</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>205.6</v>
+        <v>209.5</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.79</v>
+        <v>26.7</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.359</v>
+        <v>4.36</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.262</v>
+        <v>1.263</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.646</v>
+        <v>3.647</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.6</v>
+        <v>42.71</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.98</v>
+        <v>23.4</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.36</v>
+        <v>39.28</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.77</v>
+        <v>56.49</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.6</v>
+        <v>29.17</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46.24</v>
+        <v>45.99</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.47</v>
+        <v>29.1</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.88</v>
+        <v>21.05</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>173.01</v>
+        <v>172.5</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>190.13</v>
+        <v>189.9</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>234.28</v>
+        <v>237.6</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.863</v>
+        <v>0.866</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.93</v>
+        <v>11.66</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.09</v>
+        <v>35.68</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>27.32</v>
+        <v>27.11</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>29.63</v>
+        <v>29.7</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>44.94</v>
+        <v>44.78</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.18</v>
+        <v>33.7</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>29.98</v>
+        <v>29.01</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>209.5</v>
+        <v>204.36</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.7</v>
+        <v>26.21</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.36</v>
+        <v>4.295</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.647</v>
+        <v>3.622</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.6</v>
+        <v>42.71</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.98</v>
+        <v>23.4</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.36</v>
+        <v>39.28</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.77</v>
+        <v>56.49</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.6</v>
+        <v>29.17</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46.24</v>
+        <v>45.99</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.47</v>
+        <v>29.1</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>24.88</v>
+        <v>21.05</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>173.01</v>
+        <v>172.5</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>234.28</v>
+        <v>237.6</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>190.13</v>
+        <v>189.9</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>288.42</v>
+        <v>289.07</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.863</v>
+        <v>0.866</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.93</v>
+        <v>11.66</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.09</v>
+        <v>35.68</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>27.32</v>
+        <v>27.11</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>29.63</v>
+        <v>29.7</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>44.94</v>
+        <v>44.78</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.18</v>
+        <v>33.7</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>29.98</v>
+        <v>29.01</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>209.5</v>
+        <v>204.36</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.7</v>
+        <v>26.21</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.36</v>
+        <v>4.295</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.263</v>
+        <v>1.244</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.647</v>
+        <v>3.622</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.71</v>
+        <v>43.45</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>39.28</v>
+        <v>38.26</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.49</v>
+        <v>56.76</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.17</v>
+        <v>29.24</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.1</v>
+        <v>29.32</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.05</v>
+        <v>20.85</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>172.5</v>
+        <v>169.6</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>189.9</v>
+        <v>187.33</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>237.6</v>
+        <v>234.53</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.866</v>
+        <v>0.861</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.66</v>
+        <v>11.77</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>35.68</v>
+        <v>36.05</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>27.11</v>
+        <v>27.16</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>29.7</v>
+        <v>29.69</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>600</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>44.78</v>
+        <v>45.05</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.7</v>
+        <v>34.3</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>29.01</v>
+        <v>29.53</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>204.36</v>
+        <v>206.58</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.21</v>
+        <v>26.27</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.295</v>
+        <v>4.341</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.622</v>
+        <v>3.635</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.71</v>
+        <v>43.45</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>300</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>39.28</v>
+        <v>38.26</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.49</v>
+        <v>56.76</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.17</v>
+        <v>29.24</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.1</v>
+        <v>29.32</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.05</v>
+        <v>20.85</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>172.5</v>
+        <v>169.6</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>237.6</v>
+        <v>234.53</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>189.9</v>
+        <v>187.33</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>289.07</v>
+        <v>287.3</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.866</v>
+        <v>0.861</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.66</v>
+        <v>11.77</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>35.68</v>
+        <v>36.05</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>27.11</v>
+        <v>27.16</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>29.7</v>
+        <v>29.69</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1100</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>44.78</v>
+        <v>45.05</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.7</v>
+        <v>34.3</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>29.01</v>
+        <v>29.53</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>204.36</v>
+        <v>206.58</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.21</v>
+        <v>26.27</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.295</v>
+        <v>4.341</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.244</v>
+        <v>1.257</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.622</v>
+        <v>3.635</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -568,8 +568,8 @@
     <col width="12.625" customWidth="1" style="23" min="5" max="5"/>
     <col width="13.5" customWidth="1" style="19" min="6" max="6"/>
     <col width="9.875" customWidth="1" style="20" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="12"/>
-    <col width="9" customWidth="1" style="1" min="13" max="16384"/>
+    <col width="9" customWidth="1" style="1" min="8" max="13"/>
+    <col width="9" customWidth="1" style="1" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -619,10 +619,10 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.45</v>
+        <v>43.4</v>
       </c>
       <c r="D2" s="24" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E2" s="23">
         <f>C2*D2</f>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.8</v>
+        <v>23.77</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>38.26</v>
+        <v>37.88</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.76</v>
+        <v>56.39</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.24</v>
+        <v>29.29</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.99</v>
+        <v>46</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.32</v>
+        <v>29.62</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.85</v>
+        <v>20.86</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>169.6</v>
+        <v>170.66</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>187.33</v>
+        <v>188.9</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>234.53</v>
+        <v>234.8</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.861</v>
+        <v>0.862</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.77</v>
+        <v>12.06</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.05</v>
+        <v>36.16</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>27.16</v>
+        <v>27</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>29.69</v>
+        <v>30.28</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E17" s="23">
         <f>C17*D17</f>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>45.05</v>
+        <v>45.63</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.3</v>
+        <v>34.08</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>29.53</v>
+        <v>28.7</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>206.58</v>
+        <v>209</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.27</v>
+        <v>27.22</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.341</v>
+        <v>4.319</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.635</v>
+        <v>3.627</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1307,8 +1307,8 @@
     <col width="12.625" customWidth="1" style="23" min="5" max="5"/>
     <col width="13.5" customWidth="1" style="19" min="6" max="6"/>
     <col width="9.875" customWidth="1" style="20" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="12"/>
-    <col width="9" customWidth="1" style="1" min="13" max="16384"/>
+    <col width="9" customWidth="1" style="1" min="8" max="13"/>
+    <col width="9" customWidth="1" style="1" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1358,10 +1358,10 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.45</v>
+        <v>43.4</v>
       </c>
       <c r="D2" s="24" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E2" s="23">
         <f>C2*D2</f>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.8</v>
+        <v>23.77</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>38.26</v>
+        <v>37.88</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.76</v>
+        <v>56.39</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.24</v>
+        <v>29.29</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>45.99</v>
+        <v>46</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.32</v>
+        <v>29.62</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.85</v>
+        <v>20.86</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>169.6</v>
+        <v>170.66</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>234.53</v>
+        <v>234.8</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>187.33</v>
+        <v>188.9</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>287.3</v>
+        <v>285</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.861</v>
+        <v>0.862</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.77</v>
+        <v>12.06</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.05</v>
+        <v>36.16</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>27.16</v>
+        <v>27</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>29.69</v>
+        <v>30.28</v>
       </c>
       <c r="D18" s="24" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E18" s="23">
         <f>C18*D18</f>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>45.05</v>
+        <v>45.63</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.3</v>
+        <v>34.08</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>29.53</v>
+        <v>28.7</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>206.58</v>
+        <v>209</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.27</v>
+        <v>27.22</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.341</v>
+        <v>4.319</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.257</v>
+        <v>1.248</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.635</v>
+        <v>3.627</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.77</v>
+        <v>24.52</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.88</v>
+        <v>38.39</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.39</v>
+        <v>56.97</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.29</v>
+        <v>29.46</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46</v>
+        <v>47.06</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.62</v>
+        <v>30.5</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.86</v>
+        <v>21.53</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>170.66</v>
+        <v>172.1</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>188.9</v>
+        <v>189.11</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>234.8</v>
+        <v>235.7</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.862</v>
+        <v>0.868</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>12.06</v>
+        <v>11.99</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.16</v>
+        <v>36.5</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>27</v>
+        <v>27.21</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.28</v>
+        <v>30.85</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>700</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>45.63</v>
+        <v>46.16</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.08</v>
+        <v>34.11</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>28.7</v>
+        <v>28.39</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>209</v>
+        <v>214.95</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>27.22</v>
+        <v>29.94</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.319</v>
+        <v>4.331</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.627</v>
+        <v>3.628</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.77</v>
+        <v>24.52</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>37.88</v>
+        <v>38.39</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.39</v>
+        <v>56.97</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.29</v>
+        <v>29.46</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46</v>
+        <v>47.06</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.62</v>
+        <v>30.5</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.86</v>
+        <v>21.53</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>170.66</v>
+        <v>172.1</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>234.8</v>
+        <v>235.7</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>188.9</v>
+        <v>189.11</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>285</v>
+        <v>290.39</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.862</v>
+        <v>0.868</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>12.06</v>
+        <v>11.99</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.16</v>
+        <v>36.5</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>27</v>
+        <v>27.21</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>30.28</v>
+        <v>30.85</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>45.63</v>
+        <v>46.16</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.08</v>
+        <v>34.11</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>28.7</v>
+        <v>28.39</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>209</v>
+        <v>214.95</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>27.22</v>
+        <v>29.94</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.319</v>
+        <v>4.331</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.248</v>
+        <v>1.25</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.627</v>
+        <v>3.628</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.4</v>
+        <v>42.74</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>100</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.52</v>
+        <v>24.33</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>38.39</v>
+        <v>36.92</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.97</v>
+        <v>56.9</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.46</v>
+        <v>29.59</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>47.06</v>
+        <v>46.55</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>30.5</v>
+        <v>29.67</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.53</v>
+        <v>21.52</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>172.1</v>
+        <v>168.5</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>189.11</v>
+        <v>186.7</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>235.7</v>
+        <v>233.89</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.99</v>
+        <v>11.9</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.5</v>
+        <v>36.12</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>27.21</v>
+        <v>26.85</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.85</v>
+        <v>30.35</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>700</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>46.16</v>
+        <v>44.67</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.11</v>
+        <v>33.95</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>28.39</v>
+        <v>27.86</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>214.95</v>
+        <v>208.95</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>29.94</v>
+        <v>28.32</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.331</v>
+        <v>4.286</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.628</v>
+        <v>3.599</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.4</v>
+        <v>42.74</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.52</v>
+        <v>24.33</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>38.39</v>
+        <v>36.92</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.97</v>
+        <v>56.9</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.46</v>
+        <v>29.59</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>47.06</v>
+        <v>46.55</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>30.5</v>
+        <v>29.67</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.53</v>
+        <v>21.52</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>172.1</v>
+        <v>168.5</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>235.7</v>
+        <v>233.89</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>189.11</v>
+        <v>186.7</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>290.39</v>
+        <v>290.2</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.868</v>
+        <v>0.857</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.99</v>
+        <v>11.9</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.5</v>
+        <v>36.12</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>27.21</v>
+        <v>26.85</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>30.85</v>
+        <v>30.35</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>46.16</v>
+        <v>44.67</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.11</v>
+        <v>33.95</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>28.39</v>
+        <v>27.86</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>214.95</v>
+        <v>208.95</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>29.94</v>
+        <v>28.32</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.331</v>
+        <v>4.286</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.25</v>
+        <v>1.235</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.628</v>
+        <v>3.599</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.74</v>
+        <v>43.05</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>100</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.33</v>
+        <v>23.7</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.9</v>
+        <v>56.55</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.59</v>
+        <v>29.42</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46.55</v>
+        <v>43.76</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.67</v>
+        <v>28.88</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.52</v>
+        <v>21.15</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>168.5</v>
+        <v>170.39</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>186.7</v>
+        <v>185.91</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>233.89</v>
+        <v>232.5</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.857</v>
+        <v>0.853</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.9</v>
+        <v>11.74</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.12</v>
+        <v>36.28</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>26.85</v>
+        <v>26.41</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.35</v>
+        <v>30.13</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>700</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>44.67</v>
+        <v>44.38</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.95</v>
+        <v>33.94</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>27.86</v>
+        <v>28.15</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>208.95</v>
+        <v>214.62</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>28.32</v>
+        <v>27.05</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.286</v>
+        <v>4.289</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.599</v>
+        <v>3.65</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.74</v>
+        <v>43.05</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24.33</v>
+        <v>23.7</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.9</v>
+        <v>56.55</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.59</v>
+        <v>29.42</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46.55</v>
+        <v>43.76</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.67</v>
+        <v>28.88</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.52</v>
+        <v>21.15</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>168.5</v>
+        <v>170.39</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>233.89</v>
+        <v>232.5</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>186.7</v>
+        <v>185.91</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>290.2</v>
+        <v>290.8</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.857</v>
+        <v>0.853</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.9</v>
+        <v>11.74</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.12</v>
+        <v>36.28</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>26.85</v>
+        <v>26.41</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>30.35</v>
+        <v>30.13</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>44.67</v>
+        <v>44.38</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.95</v>
+        <v>33.94</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>27.86</v>
+        <v>28.15</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>208.95</v>
+        <v>214.62</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>28.32</v>
+        <v>27.05</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.286</v>
+        <v>4.289</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.235</v>
+        <v>1.236</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.599</v>
+        <v>3.65</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.05</v>
+        <v>42.92</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>100</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.7</v>
+        <v>23.62</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.92</v>
+        <v>36.69</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.55</v>
+        <v>56.83</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.42</v>
+        <v>29.49</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>43.76</v>
+        <v>44.05</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.15</v>
+        <v>21.39</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>170.39</v>
+        <v>171.05</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>185.91</v>
+        <v>188.08</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>232.5</v>
+        <v>233.8</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.853</v>
+        <v>0.863</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.74</v>
+        <v>11.79</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.28</v>
+        <v>36.61</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>26.41</v>
+        <v>26.46</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.13</v>
+        <v>31.15</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>700</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>44.38</v>
+        <v>45.65</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.94</v>
+        <v>34.23</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>28.15</v>
+        <v>28.5</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>214.62</v>
+        <v>219.61</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>27.05</v>
+        <v>26.5</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.289</v>
+        <v>4.271</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.65</v>
+        <v>3.663</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.05</v>
+        <v>42.92</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.7</v>
+        <v>23.62</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.92</v>
+        <v>36.69</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.55</v>
+        <v>56.83</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.42</v>
+        <v>29.49</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>43.76</v>
+        <v>44.05</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.15</v>
+        <v>21.39</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>170.39</v>
+        <v>171.05</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>232.5</v>
+        <v>233.8</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>185.91</v>
+        <v>188.08</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>290.8</v>
+        <v>292.81</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.853</v>
+        <v>0.863</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.74</v>
+        <v>11.79</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.28</v>
+        <v>36.61</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>26.41</v>
+        <v>26.46</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>30.13</v>
+        <v>31.15</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>44.38</v>
+        <v>45.65</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.94</v>
+        <v>34.23</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>28.15</v>
+        <v>28.5</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>214.62</v>
+        <v>219.61</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>27.05</v>
+        <v>26.5</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.289</v>
+        <v>4.271</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.236</v>
+        <v>1.231</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.65</v>
+        <v>3.663</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.92</v>
+        <v>43.2</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>100</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.62</v>
+        <v>23.53</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.69</v>
+        <v>36.85</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.83</v>
+        <v>57.06</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.49</v>
+        <v>29.41</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.05</v>
+        <v>46.03</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.88</v>
+        <v>29.97</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.39</v>
+        <v>20.74</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>171.05</v>
+        <v>172.89</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>188.08</v>
+        <v>190.99</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>233.8</v>
+        <v>237.38</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.863</v>
+        <v>0.871</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.79</v>
+        <v>11.76</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.61</v>
+        <v>36.58</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>26.46</v>
+        <v>26.45</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>31.15</v>
+        <v>30.93</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>700</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>45.65</v>
+        <v>46.52</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.23</v>
+        <v>34.13</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>28.5</v>
+        <v>29.17</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>219.61</v>
+        <v>219</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.5</v>
+        <v>26.77</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.271</v>
+        <v>4.3</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.663</v>
+        <v>3.668</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.92</v>
+        <v>43.2</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.62</v>
+        <v>23.53</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.69</v>
+        <v>36.85</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.83</v>
+        <v>57.06</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.49</v>
+        <v>29.41</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>44.05</v>
+        <v>46.03</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>28.88</v>
+        <v>29.97</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>21.39</v>
+        <v>20.74</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>171.05</v>
+        <v>172.89</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>233.8</v>
+        <v>237.38</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>188.08</v>
+        <v>190.99</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>292.81</v>
+        <v>296.2</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.863</v>
+        <v>0.871</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.79</v>
+        <v>11.76</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.61</v>
+        <v>36.58</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>26.46</v>
+        <v>26.45</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>31.15</v>
+        <v>30.93</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>45.65</v>
+        <v>46.52</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.23</v>
+        <v>34.13</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>28.5</v>
+        <v>29.17</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>219.61</v>
+        <v>219</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.5</v>
+        <v>26.77</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.271</v>
+        <v>4.3</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.231</v>
+        <v>1.239</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.663</v>
+        <v>3.668</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.2</v>
+        <v>42.79</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>100</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.53</v>
+        <v>23.68</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.85</v>
+        <v>36.51</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>57.06</v>
+        <v>56.85</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.41</v>
+        <v>29.29</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>800</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46.03</v>
+        <v>47.05</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.97</v>
+        <v>30.63</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.74</v>
+        <v>20.5</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>172.89</v>
+        <v>171.39</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>190.99</v>
+        <v>188.1</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>237.38</v>
+        <v>231.5</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.871</v>
+        <v>0.856</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.76</v>
+        <v>11.51</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.58</v>
+        <v>36.41</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>26.45</v>
+        <v>26.32</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.93</v>
+        <v>30.68</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>700</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>46.52</v>
+        <v>47.18</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>34.13</v>
+        <v>33.41</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>29.17</v>
+        <v>28.74</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>219</v>
+        <v>214.83</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>26.77</v>
+        <v>27.21</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.3</v>
+        <v>4.276</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.668</v>
+        <v>3.659</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>43.2</v>
+        <v>42.79</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.53</v>
+        <v>23.68</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.85</v>
+        <v>36.51</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>57.06</v>
+        <v>56.85</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>29.41</v>
+        <v>29.29</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1400</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>46.03</v>
+        <v>47.05</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>29.97</v>
+        <v>30.63</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.74</v>
+        <v>20.5</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>172.89</v>
+        <v>171.39</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>237.38</v>
+        <v>231.5</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>190.99</v>
+        <v>188.1</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>296.2</v>
+        <v>287.12</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.871</v>
+        <v>0.856</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.76</v>
+        <v>11.51</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.58</v>
+        <v>36.41</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>26.45</v>
+        <v>26.32</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>30.93</v>
+        <v>30.68</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>46.52</v>
+        <v>47.18</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>34.13</v>
+        <v>33.41</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>29.17</v>
+        <v>28.74</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>219</v>
+        <v>214.83</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>26.77</v>
+        <v>27.21</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.3</v>
+        <v>4.276</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.239</v>
+        <v>1.232</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.668</v>
+        <v>3.659</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>

--- a/账户明细.xlsx
+++ b/账户明细.xlsx
@@ -619,7 +619,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.79</v>
+        <v>42.72</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>100</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.68</v>
+        <v>23.06</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1000</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.51</v>
+        <v>37.33</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>700</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.85</v>
+        <v>56.33</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>420</v>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>47.05</v>
+        <v>46.64</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>640</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>30.63</v>
+        <v>30.35</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>200</v>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.5</v>
+        <v>20.51</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>171.39</v>
+        <v>171</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>100</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>188.1</v>
+        <v>187.12</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>231.5</v>
+        <v>229.04</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>0.856</v>
+        <v>0.854</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>8400</v>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>11.51</v>
+        <v>11.61</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1568</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>36.41</v>
+        <v>36.77</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>700</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>26.32</v>
+        <v>26.57</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>30.68</v>
+        <v>30.65</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>700</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>47.18</v>
+        <v>46.42</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>400</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>33.41</v>
+        <v>33.31</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>300</v>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>28.74</v>
+        <v>29.1</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>200</v>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>214.83</v>
+        <v>219.98</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>100</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>27.21</v>
+        <v>27.05</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>100</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>4.276</v>
+        <v>4.279</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>200</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>3.659</v>
+        <v>3.697</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>1400</v>
@@ -1358,7 +1358,7 @@
         <v>601318</v>
       </c>
       <c r="C2" s="23" t="n">
-        <v>42.79</v>
+        <v>42.72</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>200</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>23.68</v>
+        <v>23.06</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>1600</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>36.51</v>
+        <v>37.33</v>
       </c>
       <c r="D4" s="24" t="n">
         <v>1200</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56.85</v>
+        <v>56.33</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>700</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>47.05</v>
+        <v>46.64</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>1240</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>30.63</v>
+        <v>30.35</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>400</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>20.5</v>
+        <v>20.51</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>1700</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>171.39</v>
+        <v>171</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>300</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C11" s="23" t="n">
-        <v>231.5</v>
+        <v>229.04</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>100</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C12" s="23" t="n">
-        <v>188.1</v>
+        <v>187.12</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>100</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C13" s="23" t="n">
-        <v>287.12</v>
+        <v>286.28</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>140</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>0.856</v>
+        <v>0.854</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>17600</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>11.51</v>
+        <v>11.61</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>2668</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>36.41</v>
+        <v>36.77</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>1000</v>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>26.32</v>
+        <v>26.57</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>1300</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>30.68</v>
+        <v>30.65</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>1200</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>47.18</v>
+        <v>46.42</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>800</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>33.41</v>
+        <v>33.31</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>400</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>28.74</v>
+        <v>29.1</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>200</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>214.83</v>
+        <v>219.98</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>300</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>27.21</v>
+        <v>27.05</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>800</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.276</v>
+        <v>4.279</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>2800</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>1.232</v>
+        <v>1.23</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>500</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>3.659</v>
+        <v>3.697</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>4700</v>
